--- a/Datos/Datos limpios/encuesta_limpia.xlsx
+++ b/Datos/Datos limpios/encuesta_limpia.xlsx
@@ -419,22 +419,22 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>conocimiento</t>
+          <t>respeto</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>capacitacion</t>
+          <t>participacion</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>materiales</t>
+          <t>conflictos</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>aplicacion</t>
+          <t>pertenencia</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -523,7 +523,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Falta de capacitación; Recursos insuficientes</t>
+          <t>Falta de comunicación; Recursos insuficientes</t>
         </is>
       </c>
       <c r="Q2">
@@ -605,7 +605,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Infraestructura deficiente</t>
+          <t>Conflictos entre estudiantes</t>
         </is>
       </c>
       <c r="Q3">
@@ -685,6 +685,11 @@
           <t>Mucho</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sin información</t>
+        </is>
+      </c>
       <c r="Q4">
         <v>91</v>
       </c>
@@ -764,7 +769,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Resistencia al cambio; Falta de capacitación</t>
+          <t>Poca participación familiar; Falta de comunicación</t>
         </is>
       </c>
       <c r="Q5">
@@ -928,7 +933,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Infraestructura deficiente</t>
+          <t>Conflictos entre estudiantes</t>
         </is>
       </c>
       <c r="Q7">
@@ -1010,7 +1015,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Falta de capacitación</t>
+          <t>Falta de comunicación</t>
         </is>
       </c>
       <c r="Q8">
@@ -1248,7 +1253,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Infraestructura deficiente</t>
+          <t>Conflictos entre estudiantes</t>
         </is>
       </c>
       <c r="Q11">
@@ -1325,7 +1330,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Falta de capacitación</t>
+          <t>Falta de comunicación</t>
         </is>
       </c>
       <c r="Q12">
@@ -1407,7 +1412,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Resistencia al cambio</t>
+          <t>Poca participación familiar</t>
         </is>
       </c>
       <c r="Q13">
@@ -1489,7 +1494,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Falta de capacitación; Infraestructura deficiente</t>
+          <t>Falta de comunicación; Conflictos entre estudiantes</t>
         </is>
       </c>
       <c r="Q14">
@@ -1735,7 +1740,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Infraestructura deficiente</t>
+          <t>Conflictos entre estudiantes</t>
         </is>
       </c>
       <c r="Q17">
@@ -1817,7 +1822,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Falta de capacitación</t>
+          <t>Falta de comunicación</t>
         </is>
       </c>
       <c r="Q18">
@@ -1899,7 +1904,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Resistencia al cambio</t>
+          <t>Poca participación familiar</t>
         </is>
       </c>
       <c r="Q19">
@@ -1981,7 +1986,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Recursos insuficientes; Falta de capacitación</t>
+          <t>Recursos insuficientes; Falta de comunicación</t>
         </is>
       </c>
       <c r="Q20">
